--- a/data/monthly_investment_analysis.xlsx
+++ b/data/monthly_investment_analysis.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.55</v>
+        <v>3.546698086459044</v>
       </c>
       <c r="D2" t="n">
-        <v>10355</v>
+        <v>10354.6698</v>
       </c>
       <c r="E2" t="n">
-        <v>355</v>
+        <v>354.6698</v>
       </c>
       <c r="F2" t="n">
-        <v>22.7143</v>
+        <v>22.8026</v>
       </c>
       <c r="G2" t="n">
-        <v>172.6825</v>
+        <v>172.274</v>
       </c>
     </row>
     <row r="3">
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.72</v>
+        <v>1.716203487028789</v>
       </c>
       <c r="D3" t="n">
-        <v>10341.5385</v>
+        <v>10341.2148</v>
       </c>
       <c r="E3" t="n">
-        <v>341.5385</v>
+        <v>341.2148</v>
       </c>
       <c r="F3" t="n">
-        <v>67.22190000000001</v>
+        <v>67.4619</v>
       </c>
       <c r="G3" t="n">
-        <v>181.1365</v>
+        <v>180.9227</v>
       </c>
     </row>
     <row r="4">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.27</v>
+        <v>5.269086438132042</v>
       </c>
       <c r="D4" t="n">
-        <v>10619.7259</v>
+        <v>10620.1839</v>
       </c>
       <c r="E4" t="n">
-        <v>619.7259</v>
+        <v>620.1839</v>
       </c>
       <c r="F4" t="n">
-        <v>443.3619</v>
+        <v>442.9828</v>
       </c>
       <c r="G4" t="n">
-        <v>159.996</v>
+        <v>160.0351</v>
       </c>
     </row>
     <row r="5">
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.26</v>
+        <v>0.3138510451797361</v>
       </c>
       <c r="D5" t="n">
-        <v>10568.9363</v>
+        <v>10572.8574</v>
       </c>
       <c r="E5" t="n">
-        <v>568.9363</v>
+        <v>572.8574</v>
       </c>
       <c r="F5" t="n">
-        <v>275.4086</v>
+        <v>275.7028</v>
       </c>
       <c r="G5" t="n">
-        <v>216.4199</v>
+        <v>217.5665</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-2.52</v>
+        <v>-2.517390672760977</v>
       </c>
       <c r="D6" t="n">
-        <v>10171.5443</v>
+        <v>10173.3233</v>
       </c>
       <c r="E6" t="n">
-        <v>171.5443</v>
+        <v>173.3233</v>
       </c>
       <c r="F6" t="n">
-        <v>-74.13809999999999</v>
+        <v>-73.98139999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>152.0948</v>
+        <v>153.0183</v>
       </c>
     </row>
     <row r="7">
@@ -600,19 +600,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78</v>
+        <v>0.7933824522864397</v>
       </c>
       <c r="D7" t="n">
-        <v>10094.9475</v>
+        <v>10095.679</v>
       </c>
       <c r="E7" t="n">
-        <v>94.94750000000001</v>
+        <v>95.679</v>
       </c>
       <c r="F7" t="n">
-        <v>-184.5552</v>
+        <v>-183.6786</v>
       </c>
       <c r="G7" t="n">
-        <v>150.458</v>
+        <v>149.7451</v>
       </c>
     </row>
     <row r="8">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.42</v>
+        <v>2.425889051288199</v>
       </c>
       <c r="D8" t="n">
-        <v>10258.4856</v>
+        <v>10258.8773</v>
       </c>
       <c r="E8" t="n">
-        <v>258.4856</v>
+        <v>258.8773</v>
       </c>
       <c r="F8" t="n">
-        <v>-104.7283</v>
+        <v>-103.9265</v>
       </c>
       <c r="G8" t="n">
-        <v>243.6442</v>
+        <v>242.826</v>
       </c>
     </row>
     <row r="9">
@@ -650,19 +650,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.21</v>
+        <v>0.2080015870816521</v>
       </c>
       <c r="D9" t="n">
-        <v>10065.6261</v>
+        <v>10065.7161</v>
       </c>
       <c r="E9" t="n">
-        <v>65.62609999999999</v>
+        <v>65.7161</v>
       </c>
       <c r="F9" t="n">
-        <v>-190.0829</v>
+        <v>-190.3274</v>
       </c>
       <c r="G9" t="n">
-        <v>196.6109</v>
+        <v>196.814</v>
       </c>
     </row>
     <row r="10">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.46</v>
+        <v>-0.464911556765979</v>
       </c>
       <c r="D10" t="n">
-        <v>9890.011399999999</v>
+        <v>9890.1777</v>
       </c>
       <c r="E10" t="n">
-        <v>-109.9886</v>
+        <v>-109.8223</v>
       </c>
       <c r="F10" t="n">
-        <v>-332.167</v>
+        <v>-331.9689</v>
       </c>
       <c r="G10" t="n">
-        <v>208.8207</v>
+        <v>208.4555</v>
       </c>
     </row>
     <row r="11">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.2</v>
+        <v>1.196111316683557</v>
       </c>
       <c r="D11" t="n">
-        <v>9837.094999999999</v>
+        <v>9836.624599999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-162.905</v>
+        <v>-163.3754</v>
       </c>
       <c r="F11" t="n">
-        <v>-355.792</v>
+        <v>-356.0716</v>
       </c>
       <c r="G11" t="n">
-        <v>204.086</v>
+        <v>204.3861</v>
       </c>
     </row>
     <row r="12">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.43</v>
+        <v>0.4287159575631749</v>
       </c>
       <c r="D12" t="n">
-        <v>9760.2515</v>
+        <v>9758.435100000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-239.7485</v>
+        <v>-241.5649</v>
       </c>
       <c r="F12" t="n">
-        <v>-427.3649</v>
+        <v>-427.382</v>
       </c>
       <c r="G12" t="n">
-        <v>260.3534</v>
+        <v>259.3107</v>
       </c>
     </row>
     <row r="13">
@@ -750,19 +750,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.2</v>
+        <v>3.203991436420939</v>
       </c>
       <c r="D13" t="n">
-        <v>10006.2099</v>
+        <v>10005.9101</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2099</v>
+        <v>5.9101</v>
       </c>
       <c r="F13" t="n">
-        <v>-268.8599</v>
+        <v>-268.9607</v>
       </c>
       <c r="G13" t="n">
-        <v>345.9103</v>
+        <v>345.8739</v>
       </c>
     </row>
   </sheetData>
